--- a/InputData/elec/CSC/Capacity Supply Curve.xlsx
+++ b/InputData/elec/CSC/Capacity Supply Curve.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\LA\elec\CSC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\AL\elec\CSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBB5D608-B445-4114-BBF8-3E047D5B3E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{58A86371-1BB4-422C-B830-AB57620B10CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="915" yWindow="885" windowWidth="19965" windowHeight="7170" activeTab="3" xr2:uid="{F87DB1D1-DC21-4EA7-B1DF-998EE56837F8}"/>
   </bookViews>
@@ -4586,7 +4586,7 @@
         <v>29</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C1" s="3">
         <v>45532</v>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B2" t="str">
         <f>LOOKUP(B1,F1:G50,G1:G50)</f>
-        <v>LA</v>
+        <v>AL</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>94</v>
